--- a/estudios/Top 100 estudios.xlsx
+++ b/estudios/Top 100 estudios.xlsx
@@ -2,21 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f4d2ca30c99d7ee8/07. BIOS/MKT Digital/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="8_{67889C51-1E3F-4B33-A494-978096C5C1CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4893CF4-A776-4486-A159-0E3EE6E7F93B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DFD0148-3036-4FA4-8937-783AD70B1645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E4128EBF-0CD2-42A3-A95C-94C16AE8D9CA}"/>
   </bookViews>
   <sheets>
-    <sheet name="Top 100 estudios" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -28,16 +31,22 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="352">
   <si>
     <t>Tipo</t>
   </si>
   <si>
+    <t>Columna1</t>
+  </si>
+  <si>
     <t>Clave o componentes</t>
   </si>
   <si>
@@ -47,6 +56,9 @@
     <t>Entrega (días)</t>
   </si>
   <si>
+    <t>Descripción</t>
+  </si>
+  <si>
     <t>Precio</t>
   </si>
   <si>
@@ -59,18 +71,42 @@
     <t>Paquete</t>
   </si>
   <si>
+    <t>Laboratorio</t>
+  </si>
+  <si>
     <t>PB5-38 + BHC-FEM + EGO</t>
   </si>
   <si>
+    <t>Paquete de 38 elementos</t>
+  </si>
+  <si>
+    <t>Paquete de 38 elementos para mujer; química sanguínea de 38 elementos; biometría hemática completa; BHC; biometría hemática femenina; hemograma; conteo sanguíneo; examen general de orina; EGO; análisis de sangre y orina; check up completo para mujer; chequeo general femenino.</t>
+  </si>
+  <si>
     <t>Acude con ayuno de 8 a 10 horas. Durante el ayuno puedes beber agua simple. Recolecta la primera orina de la mañana en un frasco nuevo y estéril. Evita tocar el interior del frasco o de la tapa.</t>
   </si>
   <si>
+    <t>A B &amp; C</t>
+  </si>
+  <si>
     <t>PB4-27 + BHC-MASC + EGO</t>
   </si>
   <si>
+    <t>Paquete de 27 elementos</t>
+  </si>
+  <si>
+    <t>Paquete de 27 elementos para hombre; perfil bioquímico de 27 elementos; biometría hemática completa; BHC; biometría hemática masculina; hemograma; conteo sanguíneo; examen general de orina; EGO; análisis de sangre y orina; check up completo para hombre; chequeo general masculino.</t>
+  </si>
+  <si>
     <t>BHC-FEM + EGO + QSC-6</t>
   </si>
   <si>
+    <t>Paquete de 6 elementos</t>
+  </si>
+  <si>
+    <t>Paquete de análisis para mujer; biometría hemática completa; BHC; biometría hemática femenina; hemograma; conteo sanguíneo; examen general de orina; EGO; química sanguínea de 6 elementos; QSC 6; análisis de sangre y orina; check up básico femenino.</t>
+  </si>
+  <si>
     <t>Estudio</t>
   </si>
   <si>
@@ -80,18 +116,21 @@
     <t>Química Sanguínea de 6 Elementos</t>
   </si>
   <si>
+    <t>Química sanguínea de 6 elementos; química de 6; QSC 6; análisis de química sanguínea; glucosa y química sanguínea; chequeo básico de sangre.</t>
+  </si>
+  <si>
     <t>Acude con ayuno de 8 a 10 horas. Durante el ayuno puedes beber agua simple.</t>
   </si>
   <si>
-    <t>A B &amp; C</t>
-  </si>
-  <si>
     <t>EGO</t>
   </si>
   <si>
     <t>Examen General de Orina</t>
   </si>
   <si>
+    <t>Examen general de orina; EGO; análisis de orina; examen de orina; estudio de orina; prueba de orina; análisis urinario.</t>
+  </si>
+  <si>
     <t>Recolecta la primera orina de la mañana en un frasco nuevo y estéril. Evita tocar el interior del frasco o de la tapa.</t>
   </si>
   <si>
@@ -101,42 +140,60 @@
     <t>BHC. Adulto Femenino</t>
   </si>
   <si>
+    <t>Biometría hemática completa; BHC; biometría hemática femenina; biometría hemática para mujer; hemograma; conteo sanguíneo completo; análisis de células de la sangre; glóbulos rojos, glóbulos blancos y plaquetas.</t>
+  </si>
+  <si>
     <t>BHC-MASC</t>
   </si>
   <si>
     <t>BHC. Adulto Masculino</t>
   </si>
   <si>
+    <t>Biometría hemática completa; BHC; biometría hemática masculina; biometría hemática para hombre; hemograma; conteo sanguíneo completo; análisis de células de la sangre; glóbulos rojos, glóbulos blancos y plaquetas.</t>
+  </si>
+  <si>
     <t>PB5-38</t>
   </si>
   <si>
     <t>Química Sanguínea de 38 Elementos</t>
   </si>
   <si>
+    <t>Química sanguínea de 38 elementos; química de 38; perfil bioquímico completo; análisis de sangre de 38 elementos; check up de sangre; chequeo bioquímico amplio.</t>
+  </si>
+  <si>
     <t>HD-G</t>
   </si>
   <si>
     <t>Hemoglobina Glucosilada</t>
   </si>
   <si>
+    <t>Hemoglobina glucosilada; hemoglobina glicosilada; HbA1c; A1c; glucosa de 3 meses; promedio de azúcar en sangre; control de diabetes.</t>
+  </si>
+  <si>
     <t>PB4-27</t>
   </si>
   <si>
-    <t>Perfil Bioquimico de 27 Elementos</t>
-  </si>
-  <si>
     <t>PB2-12E</t>
   </si>
   <si>
     <t>Química Sanguínea de 12 Elementos</t>
   </si>
   <si>
+    <t>Química sanguínea de 12 elementos; química de 12; QSC 12; perfil bioquímico de 12 elementos; análisis de sangre de 12 elementos.</t>
+  </si>
+  <si>
+    <t>Rayos X</t>
+  </si>
+  <si>
     <t>TX-1</t>
   </si>
   <si>
     <t>Tele de Tórax (Adulto)</t>
   </si>
   <si>
+    <t>Tele de tórax; radiografía de tórax; rayos X de tórax; placa de tórax; radiografía de pecho; tele de tórax adulto.</t>
+  </si>
+  <si>
     <t>No necesitas preparación especial.</t>
   </si>
   <si>
@@ -146,12 +203,18 @@
     <t>Grupo y Factor Rh</t>
   </si>
   <si>
+    <t>Grupo sanguíneo y factor Rh; grupo y Rh; tipo de sangre; grupo sanguíneo; factor RH; saber qué tipo de sangre soy.</t>
+  </si>
+  <si>
     <t>UROCUL</t>
   </si>
   <si>
     <t>Urocultivo</t>
   </si>
   <si>
+    <t>Urocultivo; cultivo de orina; cultivo urinario; examen para infección urinaria; bacterias en orina; infección de vías urinarias.</t>
+  </si>
+  <si>
     <t>Recolecta la primera orina de la mañana. Lava previamente los genitales externos con agua y jabón, desecha el primer chorro y recoge el chorro medio en un frasco estéril. Evita tocar el interior del frasco o de la tapa.</t>
   </si>
   <si>
@@ -161,24 +224,39 @@
     <t>Electrocardiograma en Reposo con Interpretacion Cardiologica</t>
   </si>
   <si>
+    <t>Electrocardiograma en reposo; EKG; ECG; electro del corazón; electrocardiograma con interpretación cardiológica; estudio del ritmo del corazón.</t>
+  </si>
+  <si>
     <t>Báñate de forma habitual y no apliques cremas ni aceites en el pecho. Si tienes abundante vello en el pecho, retíralo antes del estudio.</t>
   </si>
   <si>
+    <t>A &amp; B</t>
+  </si>
+  <si>
+    <t>Especiales</t>
+  </si>
+  <si>
+    <t>DENCOLCA</t>
+  </si>
+  <si>
+    <t>Densitometría Osea Columna/cadera</t>
+  </si>
+  <si>
+    <t>Densitometría ósea de columna y cadera; densitometría; estudio de osteoporosis; medición de densidad ósea; DEXA; huesos columna y cadera.</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
-    <t>DENCOLCA</t>
-  </si>
-  <si>
-    <t>Densitometría Osea Columna/cadera</t>
-  </si>
-  <si>
     <t>AG.P.</t>
   </si>
   <si>
     <t>Antigeno Especifico de Prostata Clave 1472</t>
   </si>
   <si>
+    <t>Antígeno prostático específico; PSA total; antígeno de próstata; examen de próstata en sangre; prueba PSA; estudio de próstata.</t>
+  </si>
+  <si>
     <t>Acude con ayuno de 8 a 10 horas. Durante el ayuno puedes beber agua simple. Evita la eyaculación y el ejercicio intenso en bicicleta durante las 48 horas previas. Si tuviste manipulación prostática reciente, avisa al laboratorio.</t>
   </si>
   <si>
@@ -188,12 +266,18 @@
     <t>Perfil Tiroideo 1</t>
   </si>
   <si>
+    <t>Perfil tiroideo 1; perfil de tiroides; pruebas de tiroides; estudios tiroideos; hormonas tiroideas; análisis para revisar la tiroides.</t>
+  </si>
+  <si>
     <t>TP</t>
   </si>
   <si>
     <t>Tiempo de Protrombina Clave 2644</t>
   </si>
   <si>
+    <t>Tiempo de protrombina; TP; PT; tiempo de coagulación; prueba de coagulación de la sangre; protrombina.</t>
+  </si>
+  <si>
     <t>Pregunta al laboratorio cuántas horas de ayuno necesitas. Si tomas anticoagulantes, informa el nombre y horario de tu última dosis; no suspendas ningún medicamento sin indicación médica.</t>
   </si>
   <si>
@@ -203,42 +287,60 @@
     <t>Tiempo de Tromboplastina Parcial Activada (TTP) Clave 0262</t>
   </si>
   <si>
+    <t>Tiempo de tromboplastina parcial activada; TTPa; TPT; aPTT; prueba de coagulación; tiempo parcial de tromboplastina.</t>
+  </si>
+  <si>
     <t>COL-LS/ADULT</t>
   </si>
   <si>
     <t>Columna Lumbo Sacra AP. y LAT. Adulto</t>
   </si>
   <si>
+    <t>Radiografía de columna lumbosacra; rayos X columna lumbar; columna lumbosacra AP y lateral; placa de espalda baja; radiografía lumbar.</t>
+  </si>
+  <si>
+    <t>USG</t>
+  </si>
+  <si>
     <t>USG-PEL</t>
   </si>
   <si>
     <t>Ultrasonido Pélvico</t>
   </si>
   <si>
+    <t>Ultrasonido pélvico; USG pélvico; ultrasonido de pelvis; eco pélvico; ultrasonido ginecológico pélvico.</t>
+  </si>
+  <si>
     <t>Realiza tu aseo habitual antes del estudio. Lleva 1.5 litros de agua. No la bebas hasta que el personal del laboratorio te lo indique; es necesario acudir con la vejiga llena.</t>
   </si>
   <si>
-    <t>A &amp; B</t>
-  </si>
-  <si>
     <t>PIE</t>
   </si>
   <si>
     <t>Prueba Inmuno de Embarazo en Suero</t>
   </si>
   <si>
+    <t>Prueba de embarazo en sangre; prueba inmunológica de embarazo en suero; embarazo en suero; test de embarazo en sangre; hCG cualitativa.</t>
+  </si>
+  <si>
     <t>RODILLA</t>
   </si>
   <si>
     <t>Rodilla AP. y LAT.</t>
   </si>
   <si>
+    <t>Radiografía de rodilla; rayos X de rodilla; placa de rodilla; rodilla AP y lateral; RX rodilla.</t>
+  </si>
+  <si>
     <t>USG-AP</t>
   </si>
   <si>
     <t>Ultrasonido Abdomino-pélvico</t>
   </si>
   <si>
+    <t>Ultrasonido abdominopélvico; ultrasonido de abdomen y pelvis; USG abdominal y pélvico; eco abdominopélvico.</t>
+  </si>
+  <si>
     <t>Acude con ayuno de 8 a 10 horas. Durante el ayuno puedes beber agua simple. Lleva 1.5 litros de agua y no la bebas hasta que el personal del laboratorio te lo indique.</t>
   </si>
   <si>
@@ -248,12 +350,18 @@
     <t>Ultrasonido de Higado y Vias Biliares</t>
   </si>
   <si>
+    <t>Ultrasonido de hígado y vías biliares; USG hígado; ultrasonido de vesícula; ultrasonido hepatobiliar; eco de hígado y vesícula.</t>
+  </si>
+  <si>
     <t>USG-GM</t>
   </si>
   <si>
     <t>Ultrasonido Mamario Bilateral</t>
   </si>
   <si>
+    <t>Ultrasonido mamario bilateral; ultrasonido de mamas; USG mamario; ultrasonido de senos; eco mamario.</t>
+  </si>
+  <si>
     <t>Realiza tu aseo habitual antes del estudio.</t>
   </si>
   <si>
@@ -263,6 +371,9 @@
     <t>Vitamina D (25-HIDROXI) Clave 1657</t>
   </si>
   <si>
+    <t>Vitamina D 25 hidroxi; 25-OH vitamina D; prueba de vitamina D; niveles de vitamina D; vitamina D en sangre.</t>
+  </si>
+  <si>
     <t>Ayuno de 8 a 12 horas.</t>
   </si>
   <si>
@@ -272,78 +383,120 @@
     <t>Insulina</t>
   </si>
   <si>
+    <t>Insulina en sangre; prueba de insulina; niveles de insulina; insulina sérica; análisis de insulina.</t>
+  </si>
+  <si>
     <t>USG-MUSC</t>
   </si>
   <si>
     <t>Ultrasonido Músculo Esqueletico</t>
   </si>
   <si>
+    <t>Ultrasonido musculoesquelético; ultrasonido músculo esquelético; USG muscular; ultrasonido de músculo, tendón o articulación; eco musculoesquelético.</t>
+  </si>
+  <si>
     <t>MASTO</t>
   </si>
   <si>
     <t>Mastografia</t>
   </si>
   <si>
+    <t>Mastografía; mamografía; estudio de mama; rayos X de mama; estudio para revisión de senos.</t>
+  </si>
+  <si>
     <t>PIE-ADULTO</t>
   </si>
   <si>
     <t>Pie AP. y LAT. (Adulto)</t>
   </si>
   <si>
+    <t>Radiografía de pie; rayos X de pie; placa de pie; pie AP y lateral; RX pie adulto.</t>
+  </si>
+  <si>
     <t>TSH</t>
   </si>
   <si>
     <t>(TSH) Hormona Estimulante de Tiroides</t>
   </si>
   <si>
+    <t>TSH; hormona estimulante de tiroides; hormona tiroestimulante; tirotropina; prueba de TSH; análisis de tiroides.</t>
+  </si>
+  <si>
     <t>RODILLA-2</t>
   </si>
   <si>
     <t>Rodillas Comparativas AP y LAT</t>
   </si>
   <si>
+    <t>Radiografías de ambas rodillas; rodillas comparativas; rayos X de rodillas; RX bilateral de rodilla; rodillas AP y lateral.</t>
+  </si>
+  <si>
     <t>USG-TR</t>
   </si>
   <si>
     <t>Ultrasonido Transvaginal</t>
   </si>
   <si>
+    <t>Ultrasonido transvaginal; USG transvaginal; eco transvaginal; ultrasonido vaginal; ultrasonido ginecológico interno.</t>
+  </si>
+  <si>
     <t>IR-HOMA</t>
   </si>
   <si>
     <t>Indice de Resistencia Homa</t>
   </si>
   <si>
+    <t>Índice HOMA; HOMA-IR; índice de resistencia a la insulina; prueba de resistencia a la insulina; cálculo HOMA.</t>
+  </si>
+  <si>
     <t>MANO-3</t>
   </si>
   <si>
     <t>Mano AP y LAT (Adulto)</t>
   </si>
   <si>
+    <t>Radiografía de mano; rayos X de mano; placa de mano; mano AP y lateral; RX mano adulto.</t>
+  </si>
+  <si>
     <t>USG.PROST</t>
   </si>
   <si>
     <t>Ultrasonido Prostatico</t>
   </si>
   <si>
+    <t>Ultrasonido prostático; USG de próstata; ultrasonido de próstata; eco prostático; estudio de próstata por ultrasonido.</t>
+  </si>
+  <si>
     <t>USG-AB</t>
   </si>
   <si>
     <t>Ultrasonido Abdominal</t>
   </si>
   <si>
+    <t>Ultrasonido abdominal; USG abdomen; ultrasonido de abdomen; eco abdominal; ultrasonido general de abdomen.</t>
+  </si>
+  <si>
     <t>PTIR-3</t>
   </si>
   <si>
     <t>Perfil Tiroideo 3</t>
   </si>
   <si>
+    <t>Perfil tiroideo 3; perfil completo de tiroides; pruebas tiroideas; hormonas tiroideas; estudios para revisar función de la tiroides.</t>
+  </si>
+  <si>
+    <t>Tomografia</t>
+  </si>
+  <si>
     <t>TAC.CRANS</t>
   </si>
   <si>
     <t>Tomografía de Cráneo Simple</t>
   </si>
   <si>
+    <t>Tomografía de cráneo simple; TAC de cráneo; tomografía de cabeza; CT de cráneo; tomografía cerebral sin contraste.</t>
+  </si>
+  <si>
     <t>Agenda previamente tu estudio. No necesitas preparación especial.</t>
   </si>
   <si>
@@ -359,6 +512,9 @@
     <t>Tomografía de Abdomen Simple</t>
   </si>
   <si>
+    <t>Tomografía de abdomen simple; TAC abdominal simple; tomografía abdominal sin contraste; CT abdomen; tomografía de abdomen.</t>
+  </si>
+  <si>
     <t>Agenda previamente tu estudio. Acude con ayuno de 8 horas y lleva 1.5 litros de agua; bébela únicamente cuando el personal te lo indique.</t>
   </si>
   <si>
@@ -368,12 +524,18 @@
     <t>Salud Visual</t>
   </si>
   <si>
+    <t>Depende del modelo</t>
+  </si>
+  <si>
     <t>USG-OB</t>
   </si>
   <si>
     <t>Ultrasonido Obstétrico</t>
   </si>
   <si>
+    <t>Ultrasonido obstétrico; ultrasonido de embarazo; USG obstétrico; eco de embarazo; ultrasonido prenatal.</t>
+  </si>
+  <si>
     <t>Realiza tu aseo habitual. Si el embarazo es menor de 12 semanas, lleva agua y bébela cuando el personal te lo indique para acudir con la vejiga llena. Después de las 12 semanas no necesitas preparación especial.</t>
   </si>
   <si>
@@ -383,12 +545,18 @@
     <t>Perfil Hormonal Completo Femenino</t>
   </si>
   <si>
+    <t>Perfil hormonal completo femenino; perfil hormonal para mujer; hormonas femeninas; estudios hormonales ginecológicos; chequeo hormonal femenino.</t>
+  </si>
+  <si>
     <t>COLPO</t>
   </si>
   <si>
     <t>Colposcopia, Papanicolaou y C. Vaginal</t>
   </si>
   <si>
+    <t>Colposcopia, Papanicolaou y cultivo vaginal; paquete ginecológico; revisión de cuello uterino; Papanicolaou; cultivo vaginal; estudio ginecológico completo.</t>
+  </si>
+  <si>
     <t>Evita relaciones sexuales durante los 3 días previos. No uses óvulos, cremas, duchas ni otros tratamientos vaginales. Acude cuando no estés menstruando y realiza tu aseo habitual. Si estás tomando antibióticos, avisa al laboratorio antes del estudio.</t>
   </si>
   <si>
@@ -398,6 +566,9 @@
     <t>T4 Libre (Tiroxina Libre).</t>
   </si>
   <si>
+    <t>T4 libre; tiroxina libre; FT4; hormona tiroidea T4 libre; prueba de tiroides T4 libre.</t>
+  </si>
+  <si>
     <t>Acude con ayuno de 10 horas. Durante el ayuno puedes beber agua simple.</t>
   </si>
   <si>
@@ -407,66 +578,99 @@
     <t>Hombro AP (Adulto)</t>
   </si>
   <si>
+    <t>Radiografía de hombro; rayos X de hombro; placa de hombro; RX hombro AP; radiografía hombro adulto.</t>
+  </si>
+  <si>
     <t>PELV-1A</t>
   </si>
   <si>
     <t>Pelvis AP (Adulto)</t>
   </si>
   <si>
+    <t>Radiografía de pelvis; rayos X de pelvis; placa de pelvis; pelvis AP; RX pelvis adulto.</t>
+  </si>
+  <si>
     <t>TOB.DER.ADUL</t>
   </si>
   <si>
     <t>Tobillo Derecho AP. y LAT. (Adulto)</t>
   </si>
   <si>
+    <t>Radiografía de tobillo derecho; rayos X tobillo derecho; placa de tobillo; RX tobillo derecho AP y lateral.</t>
+  </si>
+  <si>
     <t>COL-CADULT</t>
   </si>
   <si>
     <t>Columna Cervical AP. y LAT. Adulto</t>
   </si>
   <si>
+    <t>Radiografía de columna cervical; rayos X de cuello; columna cervical AP y lateral; placa cervical; RX cervical.</t>
+  </si>
+  <si>
     <t>TOB.IZQ.ADUL</t>
   </si>
   <si>
     <t>Tobillo Izquierdo AP. y LAT. (Adulto)</t>
   </si>
   <si>
+    <t>Radiografía de tobillo izquierdo; rayos X tobillo izquierdo; placa de tobillo; RX tobillo izquierdo AP y lateral.</t>
+  </si>
+  <si>
     <t>USG-PB</t>
   </si>
   <si>
     <t>Ultrasonido para Partes Blandas</t>
   </si>
   <si>
+    <t>Ultrasonido de partes blandas; USG partes blandas; ultrasonido de tejidos blandos; eco de bulto o masa; ultrasonido superficial.</t>
+  </si>
+  <si>
     <t>USG-RE</t>
   </si>
   <si>
     <t>Ultrasonido Renal</t>
   </si>
   <si>
+    <t>Ultrasonido renal; ultrasonido de riñones; USG renal; eco renal; estudio de riñones por ultrasonido.</t>
+  </si>
+  <si>
     <t>USG-TIRO</t>
   </si>
   <si>
     <t>Ultrasonido Tiroideo</t>
   </si>
   <si>
+    <t>Ultrasonido tiroideo; ultrasonido de tiroides; USG tiroides; eco tiroideo; estudio de nódulos tiroideos.</t>
+  </si>
+  <si>
     <t>GLU.S</t>
   </si>
   <si>
     <t>Glucosa en Suero</t>
   </si>
   <si>
+    <t>Glucosa en suero; glucosa en sangre; azúcar en sangre; prueba de glucosa; glicemia; análisis de azúcar.</t>
+  </si>
+  <si>
     <t>HOMB-1</t>
   </si>
   <si>
     <t>Hombro AP y Oblicua Adulto</t>
   </si>
   <si>
+    <t>Radiografía de hombro AP y oblicua; rayos X de hombro; placa de hombro; RX hombro adulto.</t>
+  </si>
+  <si>
     <t>C-FAR</t>
   </si>
   <si>
     <t>Cultivo Faringeo</t>
   </si>
   <si>
+    <t>Cultivo faríngeo; cultivo de garganta; exudado faríngeo; estudio de garganta; cultivo para infección de garganta.</t>
+  </si>
+  <si>
     <t>Acude en ayuno, sin lavarte los dientes, usar enjuague bucal, comer, beber ni fumar antes de la toma. Si estás tomando antibióticos, avisa al laboratorio.</t>
   </si>
   <si>
@@ -476,24 +680,36 @@
     <t>Ecocardiograma</t>
   </si>
   <si>
+    <t>Ecocardiograma; eco del corazón; ultrasonido del corazón; ecografía cardíaca; estudio de estructura y función del corazón.</t>
+  </si>
+  <si>
     <t>T3-L</t>
   </si>
   <si>
     <t>T3 Libre (Triyodotironina Libre)</t>
   </si>
   <si>
+    <t>T3 libre; triyodotironina libre; FT3; hormona tiroidea T3 libre; prueba de tiroides T3.</t>
+  </si>
+  <si>
     <t>NITRO-S</t>
   </si>
   <si>
     <t>Nitrogeno Ureico en Suero (BUN)</t>
   </si>
   <si>
+    <t>Nitrógeno ureico en suero; BUN; nitrógeno ureico en sangre; urea BUN; prueba de función renal.</t>
+  </si>
+  <si>
     <t>CPL</t>
   </si>
   <si>
     <t>Coprologico</t>
   </si>
   <si>
+    <t>Coprológico; examen de heces; análisis de materia fecal; estudio de excremento; copro; examen coproparasitario general.</t>
+  </si>
+  <si>
     <t>Recolecta una muestra de la primera evacuación del día, aproximadamente del tamaño de una nuez, en un frasco limpio y seco. Durante las 24 horas previas evita carne roja, coliflor, pepino, brócoli, melón, plátano, manzana, aguacate, jugo de uva, pera, vitamina C y aspirina.</t>
   </si>
   <si>
@@ -503,18 +719,27 @@
     <t>Ultrasonido Testicular</t>
   </si>
   <si>
+    <t>Ultrasonido testicular; USG testicular; ultrasonido de testículos; eco escrotal; ultrasonido de escroto.</t>
+  </si>
+  <si>
     <t>VDRL</t>
   </si>
   <si>
     <t>V.D.R.L. (reacciones seroluéticas) en campo oscuro, 286</t>
   </si>
   <si>
+    <t>VDRL; prueba de sífilis; examen para sífilis; serología de sífilis; prueba sanguínea para sífilis.</t>
+  </si>
+  <si>
     <t>ALB/CREAT</t>
   </si>
   <si>
     <t>Relacion Microalbumina/creatinina en Orina Ocasional (2622)</t>
   </si>
   <si>
+    <t>Relación microalbúmina/creatinina en orina; microalbuminuria; albúmina creatinina; ACR en orina; estudio de daño renal en orina.</t>
+  </si>
+  <si>
     <t>Recolecta una muestra de orina ocasional en un frasco nuevo y estéril. Evita tocar el interior del frasco o de la tapa.</t>
   </si>
   <si>
@@ -524,60 +749,90 @@
     <t>Acs. HIV (Sida) Clave 2136</t>
   </si>
   <si>
+    <t>Prueba de VIH; HIV; prueba de sida; anticuerpos VIH; examen de VIH en sangre; test de VIH.</t>
+  </si>
+  <si>
     <t>PRENUP</t>
   </si>
   <si>
     <t>Examen Prenupcial (por Persona)</t>
   </si>
   <si>
+    <t>Examen prenupcial; estudios prenupciales; análisis antes de casarse; certificado prenupcial; pruebas de laboratorio para matrimonio.</t>
+  </si>
+  <si>
     <t>R.FEBRI</t>
   </si>
   <si>
     <t>Reacciones Febriles</t>
   </si>
   <si>
+    <t>Reacciones febriles; pruebas febriles; reacciones de Widal; prueba para tifoidea; estudio de aglutinaciones febriles.</t>
+  </si>
+  <si>
     <t>PGINEC</t>
   </si>
   <si>
     <t>Perfil Hormonal Basico(ginecologico)</t>
   </si>
   <si>
+    <t>Perfil hormonal básico ginecológico; perfil hormonal femenino; hormonas femeninas; estudios hormonales para mujer; perfil ginecológico hormonal.</t>
+  </si>
+  <si>
     <t>PIERNA-ADUL</t>
   </si>
   <si>
     <t>Pierna AP. y LAT. (Adulto)</t>
   </si>
   <si>
+    <t>Radiografía de pierna; rayos X de pierna; placa de pierna; pierna AP y lateral; RX pierna adulto.</t>
+  </si>
+  <si>
     <t>PSA-LIBRE</t>
   </si>
   <si>
     <t>Antigeno Prostatico Libre Clave 1473</t>
   </si>
   <si>
+    <t>PSA libre; antígeno prostático libre; antígeno de próstata libre; examen de próstata; prueba PSA libre.</t>
+  </si>
+  <si>
     <t>DUO COV-INF</t>
   </si>
   <si>
     <t>DUO SARSCOV2-INFLUENZA A+b</t>
   </si>
   <si>
+    <t>Prueba dúo COVID e influenza A/B; SARS-CoV-2 e influenza; prueba COVID y gripe; test COVID influenza; prueba respiratoria COVID influenza.</t>
+  </si>
+  <si>
     <t>BHC6A12A</t>
   </si>
   <si>
     <t>BHC de 6 a 12 años</t>
   </si>
   <si>
+    <t>Biometría hemática completa; BHC; biometría hemática infantil; biometría para niños de 6 a 12 años; hemograma infantil; conteo sanguíneo completo; glóbulos rojos, glóbulos blancos y plaquetas.</t>
+  </si>
+  <si>
     <t>F.B.</t>
   </si>
   <si>
     <t>Fraccion Beta (Cuantificacion Hgc)</t>
   </si>
   <si>
+    <t>Fracción beta hCG cuantitativa; beta hCG; hormona del embarazo cuantitativa; prueba de embarazo cuantitativa en sangre; niveles de hCG.</t>
+  </si>
+  <si>
     <t>TAC-ABDSC</t>
   </si>
   <si>
     <t>Tomografía de Abdomen Contrastada</t>
   </si>
   <si>
+    <t>Tomografía de abdomen contrastada; TAC abdominal con contraste; tomografía de abdomen con contraste; CT abdomen contrastado.</t>
+  </si>
+  <si>
     <t>Agenda previamente tu estudio. Acude con ayuno mínimo de 6 horas y lleva un resultado reciente de creatinina. Informa si tienes alergias al medio de contraste, enfermedad renal o posibilidad de embarazo.</t>
   </si>
   <si>
@@ -587,42 +842,63 @@
     <t>USG Renal y Vias Urinarias</t>
   </si>
   <si>
+    <t>Ultrasonido renal y vías urinarias; USG riñones y vías urinarias; ultrasonido de riñones y vejiga; eco renal y urinario.</t>
+  </si>
+  <si>
     <t>BHC1A6A</t>
   </si>
   <si>
     <t>BHC de 1 a 6 Años.</t>
   </si>
   <si>
+    <t>Biometría hemática completa; BHC; biometría hemática infantil; biometría para niños de 1 a 6 años; hemograma infantil; conteo sanguíneo completo; glóbulos rojos, glóbulos blancos y plaquetas.</t>
+  </si>
+  <si>
     <t>COL-D/ADULT</t>
   </si>
   <si>
     <t>Columna Dorsal AP. y LAT. Adulto</t>
   </si>
   <si>
+    <t>Radiografía de columna dorsal; rayos X de columna torácica; columna dorsal AP y lateral; placa de espalda media; RX dorsal.</t>
+  </si>
+  <si>
     <t>PAPS</t>
   </si>
   <si>
     <t>Papanicolaou</t>
   </si>
   <si>
+    <t>Papanicolaou; PAP; citología cervical; estudio del cuello uterino; prueba de Papanicolaou; citología cervicovaginal.</t>
+  </si>
+  <si>
     <t>PELV-2A</t>
   </si>
   <si>
     <t>Pelvis 2 Proyecciones (Adulto)</t>
   </si>
   <si>
+    <t>Radiografía de pelvis 2 proyecciones; rayos X de pelvis; placa de pelvis; RX pelvis adulto.</t>
+  </si>
+  <si>
     <t>T-4</t>
   </si>
   <si>
     <t>T4 (Total) Tiroxina Sérica Total</t>
   </si>
   <si>
+    <t>T4 total; tiroxina total; hormona tiroidea T4; prueba T4; análisis de tiroides T4 total.</t>
+  </si>
+  <si>
     <t>PDA-2</t>
   </si>
   <si>
     <t>Perfil Drogas de Abuso (2)</t>
   </si>
   <si>
+    <t>Perfil de drogas de abuso; antidoping; prueba de drogas; examen toxicológico; panel de drogas; detección de sustancias.</t>
+  </si>
+  <si>
     <t>Presenta una muestra de orina ocasional y una identificación oficial con fotografía. Si la persona es menor de edad, debe acudir con su madre, padre o tutor. La toma se realiza con protocolo de cadena de custodia.</t>
   </si>
   <si>
@@ -632,36 +908,54 @@
     <t>Abdomen Simple</t>
   </si>
   <si>
+    <t>Radiografía de abdomen simple; rayos X de abdomen; placa de abdomen; RX abdomen simple; abdomen simple.</t>
+  </si>
+  <si>
     <t>C-VAG</t>
   </si>
   <si>
     <t>Cultivo Vaginal</t>
   </si>
   <si>
+    <t>Cultivo vaginal; exudado vaginal; cultivo de secreción vaginal; estudio para infección vaginal; análisis de flujo vaginal.</t>
+  </si>
+  <si>
     <t>EKG</t>
   </si>
   <si>
     <t>Electrocardiograma</t>
   </si>
   <si>
+    <t>Electrocardiograma; EKG; ECG; electro del corazón; estudio del ritmo cardíaco; prueba del corazón.</t>
+  </si>
+  <si>
     <t>T3 TOTAL</t>
   </si>
   <si>
     <t>T3 Total</t>
   </si>
   <si>
+    <t>T3 total; triyodotironina total; hormona tiroidea T3; prueba T3; análisis de tiroides T3 total.</t>
+  </si>
+  <si>
     <t>CR-CPK</t>
   </si>
   <si>
     <t>Creatin-fosfokinasa (CPK) Clave 048</t>
   </si>
   <si>
+    <t>Creatinfosfoquinasa; creatina fosfoquinasa; CPK; CK; enzima muscular; prueba de daño muscular.</t>
+  </si>
+  <si>
     <t>SOH</t>
   </si>
   <si>
     <t>Sangre Oculta en Heces</t>
   </si>
   <si>
+    <t>Sangre oculta en heces; prueba de sangre en excremento; sangre oculta fecal; FOBT; análisis de heces para sangre.</t>
+  </si>
+  <si>
     <t>Recolecta una pequeña muestra de heces en un frasco limpio, seco y de boca ancha. Evita contaminarla con orina o agua del sanitario.</t>
   </si>
   <si>
@@ -671,18 +965,27 @@
     <t>Testosterona Total Mas Libre.</t>
   </si>
   <si>
+    <t>Testosterona total y libre; testosterona en sangre; niveles de testosterona; perfil de testosterona; hormona masculina.</t>
+  </si>
+  <si>
     <t>PPRE-2</t>
   </si>
   <si>
     <t>Perfil Prenatal 2</t>
   </si>
   <si>
+    <t>Perfil prenatal 2; estudios prenatales; análisis de embarazo; chequeo prenatal; paquete de laboratorio para embarazada.</t>
+  </si>
+  <si>
     <t>TX-2ADUL</t>
   </si>
   <si>
     <t>Tele de Tórax Pa y LAT (Adulto)</t>
   </si>
   <si>
+    <t>Tele de tórax PA y lateral; radiografía de tórax dos proyecciones; rayos X de pecho; placa de tórax; RX tórax adulto.</t>
+  </si>
+  <si>
     <t>PDA-1</t>
   </si>
   <si>
@@ -695,48 +998,72 @@
     <t>Acs. Anti-hepatitis C Clave 1452</t>
   </si>
   <si>
+    <t>Anticuerpos anti hepatitis C; anti-HCV; prueba de hepatitis C; anticuerpos VHC; examen de hepatitis C en sangre.</t>
+  </si>
+  <si>
     <t>HFE</t>
   </si>
   <si>
     <t>(FSH) Hormona Folículo Estimulante</t>
   </si>
   <si>
+    <t>FSH; hormona folículo estimulante; hormona foliculoestimulante; prueba FSH; estudio de fertilidad; hormona reproductiva.</t>
+  </si>
+  <si>
     <t>HLUT</t>
   </si>
   <si>
     <t>(LH) Hormona Luteinizante</t>
   </si>
   <si>
+    <t>LH; hormona luteinizante; prueba LH; estudio de ovulación; hormona reproductiva; análisis de fertilidad.</t>
+  </si>
+  <si>
     <t>MHEP-B</t>
   </si>
   <si>
     <t>Ag. de Superficie Hepatitis B (Hbs Ag) Clave 1470</t>
   </si>
   <si>
+    <t>Antígeno de superficie de hepatitis B; HBsAg; prueba de hepatitis B; antígeno HBs; examen de hepatitis B en sangre.</t>
+  </si>
+  <si>
     <t>VPH-PCR</t>
   </si>
   <si>
     <t>Vph-pcr Clave 2120</t>
   </si>
   <si>
+    <t>PCR para VPH; prueba de virus del papiloma humano; VPH por PCR; HPV PCR; detección de papiloma humano.</t>
+  </si>
+  <si>
     <t>PIE-O</t>
   </si>
   <si>
     <t>Prueba Inmuno de Embarazo en Orina</t>
   </si>
   <si>
+    <t>Prueba de embarazo en orina; test de embarazo en orina; prueba inmunológica de embarazo; hCG en orina.</t>
+  </si>
+  <si>
     <t>COLPO-VAG</t>
   </si>
   <si>
     <t>Colposcopia y Cultivo Vaginal</t>
   </si>
   <si>
+    <t>Colposcopia y cultivo vaginal; revisión ginecológica; estudio de cuello uterino; cultivo vaginal; examen para infección vaginal.</t>
+  </si>
+  <si>
     <t>EKG-ESF</t>
   </si>
   <si>
     <t>Electrocardiograma con Esfuerzo</t>
   </si>
   <si>
+    <t>Electrocardiograma con esfuerzo; prueba de esfuerzo; EKG de esfuerzo; ECG de esfuerzo; prueba de corazón en ejercicio; ergometría.</t>
+  </si>
+  <si>
     <t>Usa ropa cómoda y tenis. Come algo ligero de 2 a 3 horas antes, evita café, bebidas energéticas, alcohol y tabaco. Lleva la indicación médica y pregunta si debes modificar algún medicamento; no lo suspendas por tu cuenta.</t>
   </si>
   <si>
@@ -746,40 +1073,28 @@
     <t>Perfil Hormonal Masculino</t>
   </si>
   <si>
+    <t>Perfil hormonal masculino; hormonas masculinas; estudios hormonales para hombre; chequeo hormonal masculino; perfil de hormonas en sangre.</t>
+  </si>
+  <si>
     <t>PPRE1</t>
   </si>
   <si>
     <t>Perfil Prenatal 1</t>
   </si>
   <si>
-    <t>Check-up completo  de 38 elementos</t>
-  </si>
-  <si>
-    <t>Check-up completo  de 27 elementos</t>
-  </si>
-  <si>
-    <t>Check-up básico  de 6 elementos</t>
-  </si>
-  <si>
-    <t>Depende del modelo</t>
-  </si>
-  <si>
-    <t>Columna1</t>
-  </si>
-  <si>
-    <t>Laboratorio</t>
-  </si>
-  <si>
-    <t>Rayos X</t>
-  </si>
-  <si>
-    <t>Especiales</t>
-  </si>
-  <si>
-    <t>USG</t>
-  </si>
-  <si>
-    <t>Tomografia</t>
+    <t>Perfil prenatal 1; estudios prenatales; análisis de embarazo; chequeo prenatal; paquete de laboratorio para embarazada.</t>
+  </si>
+  <si>
+    <t>Quimica sanguinea de 27 Elementos</t>
+  </si>
+  <si>
+    <t>Quimica sanguinea de 17 elementos; perfil bioquímico de 27 elementos; química sanguínea de 27 elementos; química de 27; análisis de sangre de 27 elementos; check up bioquímico; chequeo general de sangre.</t>
+  </si>
+  <si>
+    <t>Creatinina en suero; creatinina en sangre; prueba de creatinina; función renal; estudio de riñón en sangre, estudio para las tomografias</t>
+  </si>
+  <si>
+    <t>Salud visual; examen de la vista; revisión de la vista; valoración visual; chequeo de visión; examen visual; lentes</t>
   </si>
 </sst>
 </file>
@@ -793,7 +1108,17 @@
   <fonts count="4">
     <font>
       <sz val="11"/>
-      <name val="Carlito"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -802,11 +1127,6 @@
       <name val="Carlito"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
@@ -824,14 +1144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -842,11 +1155,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -855,57 +1168,36 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="2">
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -921,26 +1213,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Top100Paquetes" displayName="Top100Paquetes" ref="A1:H104" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H104" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tipo" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{E3D14709-A9BB-448D-BBEF-454005E444A3}" name="Columna1" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Clave o componentes" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Nombre" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Entrega (días)" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Precio" dataDxfId="3" dataCellStyle="Moneda"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Preparación para el paciente" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Sucursal" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A3D63D7D-0DE4-427F-9C14-477567E3EBCB}" name="Top100Paquetes" displayName="Top100Paquetes" ref="A1:I104" totalsRowShown="0">
+  <autoFilter ref="A1:I104" xr:uid="{A3D63D7D-0DE4-427F-9C14-477567E3EBCB}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{E4ADF4C3-C081-443E-9360-79A2A85E0B56}" name="Tipo"/>
+    <tableColumn id="2" xr3:uid="{F41BBE54-2584-4B6F-9393-CF9D13950D54}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{DC47A430-4A04-4FFE-8D58-CB25DED5C669}" name="Clave o componentes"/>
+    <tableColumn id="4" xr3:uid="{F8CCD797-7E5C-4EAE-A430-03E104F7F7B9}" name="Nombre"/>
+    <tableColumn id="5" xr3:uid="{117CEF56-7804-43A2-AD57-9A1B04FB0705}" name="Entrega (días)"/>
+    <tableColumn id="9" xr3:uid="{07319DDB-6F35-49AD-B8AF-E4A1ACAB8130}" name="Descripción" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{9D781DAB-8282-4E69-BD6D-FBA3F9402997}" name="Precio" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{B4AF8B44-9367-4255-98AC-5853FD343E79}" name="Preparación para el paciente"/>
+    <tableColumn id="8" xr3:uid="{5FBD0A0E-C5D8-475C-AED1-12050B234576}" name="Sucursal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="ChatGPT">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -980,68 +1273,162 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="ChatGPT">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
-                <a:lumMod val="102000"/>
-                <a:satMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:lumMod val="100000"/>
-                <a:satMod val="110000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1049,23 +1436,26 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1077,7 +1467,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1095,22 +1485,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
-                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1125,2734 +1515,3065 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0A43D9A-56DF-451A-9F80-93FFAB077977}">
+  <dimension ref="A1:I104"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="28.25" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="4" max="4" width="23.7265625" customWidth="1"/>
+    <col min="6" max="6" width="65.7265625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20" customHeight="1">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>243</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="58">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>239</v>
+        <v>12</v>
       </c>
       <c r="E2" s="3">
         <v>1</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="4">
         <v>930</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="58">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>240</v>
+        <v>17</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="4">
         <v>810</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="58">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="B4" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>241</v>
+        <v>19</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E4" s="3">
         <v>1</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="4">
         <v>430</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="29">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3">
         <v>1</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="4">
         <v>325</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="29">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3">
         <v>1</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="4">
         <v>85</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="43.5">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3">
         <v>1</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="4">
         <v>135</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="43.5">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E8" s="3">
         <v>1</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="4">
         <v>135</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="43.5">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E9" s="3">
         <v>1</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="4">
         <v>1090</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="29">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="4">
+        <v>280</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1</v>
-      </c>
-      <c r="F10" s="6">
-        <v>280</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="43.5">
       <c r="A11" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>348</v>
       </c>
       <c r="E11" s="3">
         <v>1</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="G11" s="4">
         <v>960</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="29">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E12" s="3">
         <v>1</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="4">
         <v>560</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="29">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E13" s="3">
         <v>1</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="4">
         <v>370</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="29">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="4">
         <v>95</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="29">
       <c r="A15" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E15" s="3">
         <v>8</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="4">
         <v>320</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>58</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="43.5">
       <c r="A16" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E16" s="3">
         <v>1</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="4">
         <v>320</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>62</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="29">
       <c r="A17" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>246</v>
+        <v>64</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="E17" s="3">
         <v>1</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="4">
         <v>500</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="29">
       <c r="A18" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="4">
+        <v>260</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="29">
+      <c r="A19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="4">
+        <v>670</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="29">
+      <c r="A20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="4">
+        <v>145</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="29">
+      <c r="A21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="4">
+        <v>145</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="29">
+      <c r="A22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="3">
-        <v>1</v>
-      </c>
-      <c r="F18" s="6">
-        <v>260</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="3">
-        <v>1</v>
-      </c>
-      <c r="F19" s="6">
-        <v>670</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="C22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="4">
+        <v>635</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1</v>
-      </c>
-      <c r="F20" s="6">
-        <v>145</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1</v>
-      </c>
-      <c r="F21" s="6">
-        <v>145</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1</v>
-      </c>
-      <c r="F22" s="6">
-        <v>635</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="29">
       <c r="A23" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="4">
         <v>500</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="H23" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>90</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="29">
       <c r="A24" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G24" s="4">
+        <v>180</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E24" s="3">
-        <v>1</v>
-      </c>
-      <c r="F24" s="6">
-        <v>180</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+    </row>
+    <row r="25" spans="1:9" ht="29">
       <c r="A25" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="E25" s="3">
         <v>1</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G25" s="4">
         <v>330</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="29">
       <c r="A26" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E26" s="3">
         <v>0</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G26" s="4">
         <v>1050</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="H26" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>100</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="29">
       <c r="A27" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="E27" s="3">
         <v>0</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G27" s="4">
         <v>500</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H27" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="29">
       <c r="A28" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="E28" s="3">
         <v>0</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" s="4">
         <v>505</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="H28" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>107</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="29">
       <c r="A29" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E29" s="3">
         <v>2</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" s="4">
         <v>800</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>111</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="29">
       <c r="A30" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="E30" s="3">
         <v>1</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G30" s="4">
         <v>315</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H30" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="43.5">
       <c r="A31" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="E31" s="3">
         <v>1</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G31" s="4">
         <v>1125</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="H31" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>107</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="29">
       <c r="A32" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>246</v>
+        <v>64</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G32" s="4">
         <v>450</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H32" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E33" s="3">
         <v>1</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G33" s="4">
         <v>330</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H33" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="29">
       <c r="A34" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="E34" s="3">
         <v>1</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" s="4">
         <v>180</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H34" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="29">
       <c r="A35" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" s="4">
         <v>590</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H35" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="29">
       <c r="A36" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="E36" s="3">
         <v>0</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="G36" s="4">
         <v>580</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="H36" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>107</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="29">
       <c r="A37" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="E37" s="3">
         <v>1</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" s="4">
         <v>300</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H37" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="29">
       <c r="A38" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="E38" s="3">
         <v>1</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G38" s="4">
         <v>320</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H38" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="29">
       <c r="A39" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="E39" s="3">
         <v>0</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G39" s="4">
         <v>520</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="H39" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>90</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="29">
       <c r="A40" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
       <c r="E40" s="3">
         <v>0</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G40" s="4">
         <v>720</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H40" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="29">
       <c r="A41" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="E41" s="3">
         <v>2</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="G41" s="4">
         <v>1400</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H41" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="29">
       <c r="A42" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>248</v>
+        <v>148</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="G42" s="4">
         <v>1800</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="H42" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>152</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="29">
       <c r="A43" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="E43" s="3">
         <v>1</v>
       </c>
-      <c r="F43" s="6">
+      <c r="F43" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="G43" s="4">
         <v>50</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H43" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="29">
       <c r="A44" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>248</v>
+        <v>148</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>106</v>
+        <v>155</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="E44" s="3">
         <v>0</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="G44" s="4">
         <v>1900</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="H44" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>158</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="29">
       <c r="A45" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>246</v>
+        <v>64</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="E45" s="3">
         <v>1</v>
       </c>
-      <c r="F45" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>34</v>
+      <c r="F45" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="29">
       <c r="A46" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="E46" s="3">
         <v>0</v>
       </c>
-      <c r="F46" s="6">
+      <c r="F46" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="G46" s="4">
         <v>510</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="H46" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>165</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="29">
       <c r="A47" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="E47" s="3">
         <v>1</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F47" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="G47" s="4">
         <v>1500</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H47" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="29">
       <c r="A48" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>246</v>
+        <v>64</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="E48" s="3">
         <v>8</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="G48" s="4">
         <v>730</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="H48" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>172</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="E49" s="3">
         <v>1</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F49" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G49" s="4">
         <v>140</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="H49" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>176</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="29">
       <c r="A50" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>122</v>
+        <v>177</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>123</v>
+        <v>178</v>
       </c>
       <c r="E50" s="3">
         <v>1</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="G50" s="4">
         <v>320</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H50" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="29">
       <c r="A51" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="E51" s="3">
         <v>1</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G51" s="4">
         <v>320</v>
       </c>
-      <c r="G51" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H51" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="29">
       <c r="A52" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="E52" s="3">
         <v>1</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="G52" s="4">
         <v>320</v>
       </c>
-      <c r="G52" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H52" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="29">
       <c r="A53" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>128</v>
+        <v>186</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="E53" s="3">
         <v>1</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="G53" s="4">
         <v>570</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H53" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="29">
       <c r="A54" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="E54" s="3">
         <v>1</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="G54" s="4">
         <v>320</v>
       </c>
-      <c r="G54" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H54" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="29">
       <c r="A55" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="E55" s="3">
         <v>0</v>
       </c>
-      <c r="F55" s="6">
+      <c r="F55" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="G55" s="4">
         <v>510</v>
       </c>
-      <c r="G55" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="H55" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>107</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="29">
       <c r="A56" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>135</v>
+        <v>196</v>
       </c>
       <c r="E56" s="3">
         <v>0</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G56" s="4">
         <v>510</v>
       </c>
-      <c r="G56" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="H56" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>90</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="29">
       <c r="A57" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>136</v>
+        <v>198</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>137</v>
+        <v>199</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
       </c>
-      <c r="F57" s="6">
+      <c r="F57" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="G57" s="4">
         <v>510</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="H57" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>107</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="29">
       <c r="A58" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>138</v>
+        <v>201</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>139</v>
+        <v>202</v>
       </c>
       <c r="E58" s="3">
         <v>1</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F58" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="G58" s="4">
         <v>90</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H58" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="29">
       <c r="A59" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>140</v>
+        <v>204</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>141</v>
+        <v>205</v>
       </c>
       <c r="E59" s="3">
         <v>1</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F59" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="G59" s="4">
         <v>510</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H59" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="29">
       <c r="A60" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>142</v>
+        <v>207</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>143</v>
+        <v>208</v>
       </c>
       <c r="E60" s="3">
         <v>8</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F60" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G60" s="4">
         <v>290</v>
       </c>
-      <c r="G60" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="H60" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>210</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="29">
       <c r="A61" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>246</v>
+        <v>64</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>146</v>
+        <v>212</v>
       </c>
       <c r="E61" s="3">
         <v>1</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F61" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="G61" s="4">
         <v>2655</v>
       </c>
-      <c r="G61" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="H61" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>107</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="29">
       <c r="A62" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>147</v>
+        <v>214</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>148</v>
+        <v>215</v>
       </c>
       <c r="E62" s="3">
         <v>1</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F62" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="G62" s="4">
         <v>140</v>
       </c>
-      <c r="G62" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="H62" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>176</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="29">
       <c r="A63" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="E63" s="3">
         <v>1</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F63" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="G63" s="4">
         <v>85</v>
       </c>
-      <c r="G63" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H63" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="29">
       <c r="A64" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>152</v>
+        <v>221</v>
       </c>
       <c r="E64" s="3">
         <v>1</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="G64" s="4">
         <v>220</v>
       </c>
-      <c r="G64" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="H64" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>223</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="29">
       <c r="A65" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>154</v>
+        <v>224</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>155</v>
+        <v>225</v>
       </c>
       <c r="E65" s="3">
         <v>0</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="G65" s="4">
         <v>510</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="H65" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>107</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="29">
       <c r="A66" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>156</v>
+        <v>227</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="E66" s="3">
         <v>1</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="G66" s="4">
         <v>110</v>
       </c>
-      <c r="G66" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H66" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="29">
       <c r="A67" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>158</v>
+        <v>230</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>159</v>
+        <v>231</v>
       </c>
       <c r="E67" s="3">
         <v>2</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F67" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G67" s="4">
         <v>120</v>
       </c>
-      <c r="G67" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="H67" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+        <v>233</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="29">
       <c r="A68" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E68" s="3">
+        <v>1</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="G68" s="4">
+        <v>320</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="29">
+      <c r="A69" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E69" s="3">
+        <v>1</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="G69" s="4">
+        <v>190</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="29">
+      <c r="A70" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E70" s="3">
+        <v>1</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G70" s="4">
+        <v>120</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="29">
+      <c r="A71" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E68" s="3">
-        <v>1</v>
-      </c>
-      <c r="F68" s="6">
+      <c r="E71" s="3">
+        <v>1</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="G71" s="4">
+        <v>950</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="29">
+      <c r="A72" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="G72" s="4">
         <v>320</v>
       </c>
-      <c r="G68" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E69" s="3">
-        <v>1</v>
-      </c>
-      <c r="F69" s="6">
-        <v>190</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E70" s="3">
-        <v>1</v>
-      </c>
-      <c r="F70" s="6">
-        <v>120</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E71" s="3">
-        <v>1</v>
-      </c>
-      <c r="F71" s="6">
-        <v>950</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E72" s="3">
-        <v>1</v>
-      </c>
-      <c r="F72" s="6">
-        <v>320</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H72" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="29">
       <c r="A73" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>171</v>
+        <v>249</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>172</v>
+        <v>250</v>
       </c>
       <c r="E73" s="3">
         <v>2</v>
       </c>
-      <c r="F73" s="6">
+      <c r="F73" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="G73" s="4">
         <v>380</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="H73" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+        <v>72</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="29">
       <c r="A74" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>173</v>
+        <v>252</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>174</v>
+        <v>253</v>
       </c>
       <c r="E74" s="3">
         <v>1</v>
       </c>
-      <c r="F74" s="6">
+      <c r="F74" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="G74" s="4">
         <v>500</v>
       </c>
-      <c r="G74" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H74" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="43.5">
       <c r="A75" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>175</v>
+        <v>255</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>176</v>
+        <v>256</v>
       </c>
       <c r="E75" s="3">
         <v>1</v>
       </c>
-      <c r="F75" s="6">
+      <c r="F75" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="G75" s="4">
         <v>135</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H75" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="29">
       <c r="A76" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>177</v>
+        <v>258</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>178</v>
+        <v>259</v>
       </c>
       <c r="E76" s="3">
         <v>1</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F76" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="G76" s="2" t="s">
-        <v>15</v>
+      <c r="G76" s="4">
+        <v>260</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="29">
       <c r="A77" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>248</v>
+        <v>148</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>179</v>
+        <v>261</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>180</v>
+        <v>262</v>
       </c>
       <c r="E77" s="3">
         <v>0</v>
       </c>
-      <c r="F77" s="6">
+      <c r="F77" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="G77" s="4">
         <v>2900</v>
       </c>
-      <c r="G77" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="H77" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
+        <v>264</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="29">
       <c r="A78" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>182</v>
+        <v>265</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>183</v>
+        <v>266</v>
       </c>
       <c r="E78" s="3">
         <v>1</v>
       </c>
-      <c r="F78" s="6">
+      <c r="F78" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="G78" s="4">
         <v>715</v>
       </c>
-      <c r="G78" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="H78" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+        <v>90</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="43.5">
       <c r="A79" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>184</v>
+        <v>268</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>185</v>
+        <v>269</v>
       </c>
       <c r="E79" s="3">
         <v>1</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G79" s="4">
         <v>135</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H79" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="29">
       <c r="A80" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>186</v>
+        <v>271</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>187</v>
+        <v>272</v>
       </c>
       <c r="E80" s="3">
         <v>1</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F80" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="G80" s="4">
         <v>570</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H80" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="29">
       <c r="A81" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>246</v>
+        <v>64</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>188</v>
+        <v>274</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>189</v>
+        <v>275</v>
       </c>
       <c r="E81" s="3">
         <v>7</v>
       </c>
-      <c r="F81" s="6">
+      <c r="F81" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="G81" s="4">
         <v>260</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="H81" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
+        <v>172</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="29">
       <c r="A82" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>190</v>
+        <v>277</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>191</v>
+        <v>278</v>
       </c>
       <c r="E82" s="3">
         <v>1</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F82" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="G82" s="4">
         <v>570</v>
       </c>
-      <c r="G82" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H82" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="29">
       <c r="A83" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>193</v>
+        <v>281</v>
       </c>
       <c r="E83" s="3">
         <v>1</v>
       </c>
-      <c r="F83" s="6">
+      <c r="F83" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="G83" s="4">
         <v>140</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="H83" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+        <v>176</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="29">
       <c r="A84" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>194</v>
+        <v>283</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>195</v>
+        <v>284</v>
       </c>
       <c r="E84" s="3">
         <v>1</v>
       </c>
-      <c r="F84" s="6">
+      <c r="F84" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="G84" s="4">
         <v>650</v>
       </c>
-      <c r="G84" s="2" t="s">
-        <v>196</v>
-      </c>
       <c r="H84" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+        <v>286</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="29">
       <c r="A85" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>197</v>
+        <v>287</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>198</v>
+        <v>288</v>
       </c>
       <c r="E85" s="3">
         <v>1</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F85" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="G85" s="4">
         <v>380</v>
       </c>
-      <c r="G85" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H85" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="29">
       <c r="A86" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>199</v>
+        <v>290</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>200</v>
+        <v>291</v>
       </c>
       <c r="E86" s="3">
         <v>8</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F86" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="G86" s="4">
         <v>390</v>
       </c>
-      <c r="G86" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="H86" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+        <v>172</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="29">
       <c r="A87" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>246</v>
+        <v>64</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>201</v>
+        <v>293</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>202</v>
+        <v>294</v>
       </c>
       <c r="E87" s="3">
         <v>0</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="G87" s="4">
         <v>210</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="H87" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
+        <v>62</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="29">
       <c r="A88" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>203</v>
+        <v>296</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>204</v>
+        <v>297</v>
       </c>
       <c r="E88" s="3">
         <v>1</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="G88" s="4">
         <v>125</v>
       </c>
-      <c r="G88" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="H88" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
+        <v>176</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="29">
       <c r="A89" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>205</v>
+        <v>299</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>206</v>
+        <v>300</v>
       </c>
       <c r="E89" s="3">
         <v>2</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F89" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="G89" s="4">
         <v>280</v>
       </c>
-      <c r="G89" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H89" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="29">
       <c r="A90" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>207</v>
+        <v>302</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>208</v>
+        <v>303</v>
       </c>
       <c r="E90" s="3">
         <v>1</v>
       </c>
-      <c r="F90" s="6">
+      <c r="F90" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="G90" s="4">
         <v>65</v>
       </c>
-      <c r="G90" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="H90" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
+        <v>305</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="29">
       <c r="A91" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>210</v>
+        <v>306</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>211</v>
+        <v>307</v>
       </c>
       <c r="E91" s="3">
         <v>2</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F91" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="G91" s="4">
         <v>420</v>
       </c>
-      <c r="G91" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="H91" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
+        <v>176</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="29">
       <c r="A92" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>212</v>
+        <v>309</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>213</v>
+        <v>310</v>
       </c>
       <c r="E92" s="3">
         <v>1</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="G92" s="4">
         <v>750</v>
       </c>
-      <c r="G92" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="H92" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="29">
       <c r="A93" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>214</v>
+        <v>312</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>215</v>
+        <v>313</v>
       </c>
       <c r="E93" s="3">
         <v>1</v>
       </c>
-      <c r="F93" s="6">
+      <c r="F93" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="G93" s="4">
         <v>590</v>
       </c>
-      <c r="G93" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H93" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
+        <v>51</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="29">
       <c r="A94" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>216</v>
+        <v>315</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>217</v>
+        <v>316</v>
       </c>
       <c r="E94" s="3">
         <v>1</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F94" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="G94" s="4">
         <v>380</v>
       </c>
-      <c r="G94" s="2" t="s">
-        <v>196</v>
-      </c>
       <c r="H94" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
+        <v>286</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="29">
       <c r="A95" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>218</v>
+        <v>317</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>219</v>
+        <v>318</v>
       </c>
       <c r="E95" s="3">
         <v>2</v>
       </c>
-      <c r="F95" s="6">
+      <c r="F95" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="G95" s="4">
         <v>600</v>
       </c>
-      <c r="G95" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H95" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="29">
       <c r="A96" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>221</v>
+        <v>321</v>
       </c>
       <c r="E96" s="3">
         <v>1</v>
       </c>
-      <c r="F96" s="6">
+      <c r="F96" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="G96" s="4">
         <v>130</v>
       </c>
-      <c r="G96" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H96" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="29">
       <c r="A97" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B97" s="8" t="s">
-        <v>244</v>
+        <v>22</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>222</v>
+        <v>323</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>223</v>
+        <v>324</v>
       </c>
       <c r="E97" s="3">
         <v>1</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="G97" s="4">
         <v>130</v>
       </c>
-      <c r="G97" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H97" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="29">
       <c r="A98" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>224</v>
+        <v>326</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>225</v>
+        <v>327</v>
       </c>
       <c r="E98" s="3">
         <v>2</v>
       </c>
-      <c r="F98" s="6">
+      <c r="F98" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="G98" s="4">
         <v>510</v>
       </c>
-      <c r="G98" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H98" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
+        <v>26</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="29">
       <c r="A99" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>226</v>
+        <v>329</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>227</v>
+        <v>330</v>
       </c>
       <c r="E99" s="3">
         <v>10</v>
       </c>
-      <c r="F99" s="6">
+      <c r="F99" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="G99" s="4">
         <v>2100</v>
       </c>
-      <c r="G99" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="H99" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
+        <v>172</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="29">
       <c r="A100" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>228</v>
+        <v>332</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>229</v>
+        <v>333</v>
       </c>
       <c r="E100" s="3">
         <v>1</v>
       </c>
-      <c r="F100" s="6">
+      <c r="F100" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="G100" s="4">
         <v>150</v>
       </c>
-      <c r="G100" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="H100" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
+        <v>30</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="29">
       <c r="A101" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>246</v>
+        <v>64</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>230</v>
+        <v>335</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>231</v>
+        <v>336</v>
       </c>
       <c r="E101" s="3">
         <v>8</v>
       </c>
-      <c r="F101" s="6">
+      <c r="F101" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="G101" s="4">
         <v>530</v>
       </c>
-      <c r="G101" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="H101" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
+        <v>172</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="29">
       <c r="A102" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>246</v>
+        <v>64</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>232</v>
+        <v>338</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>233</v>
+        <v>339</v>
       </c>
       <c r="E102" s="3">
         <v>2</v>
       </c>
-      <c r="F102" s="6">
+      <c r="F102" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="G102" s="4">
         <v>1500</v>
       </c>
-      <c r="G102" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="H102" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
+        <v>341</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="29">
       <c r="A103" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>235</v>
+        <v>342</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>236</v>
+        <v>343</v>
       </c>
       <c r="E103" s="3">
         <v>1</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F103" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="G103" s="4">
         <v>800</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="H103" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
-      <c r="A104" s="4" t="s">
-        <v>12</v>
+        <v>26</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="29">
+      <c r="A104" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E104" s="5">
-        <v>1</v>
-      </c>
-      <c r="F104" s="7">
+        <v>10</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E104" s="3">
+        <v>1</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="G104" s="6">
         <v>550</v>
       </c>
-      <c r="G104" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>16</v>
+      <c r="H104" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>